--- a/esyluban/examples/dev/DataTables/test/composite_tables2.xlsx
+++ b/esyluban/examples/dev/DataTables/test/composite_tables2.xlsx
@@ -425,7 +425,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>full_name="test.TbCompositeJsonTable1" &amp; value_type="test.CompositeJsonTable1" &amp; read_schema_from_file="false" &amp; input="*table1@test/composite_tables.json,*@test/composite_tables2.json" &amp; output="test_tbcompositejsontable1"</t>
+          <t>full_name="test.TbCompositeJsonTable1" &amp; input="*table1@test/composite_tables.json,*@test/composite_tables2.json"</t>
         </is>
       </c>
     </row>
@@ -482,7 +482,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>full_name="test.TbCompositeJsonTable2" &amp; value_type="test.CompositeJsonTable2" &amp; read_schema_from_file="false" &amp; input="*table2@test/composite_tables.json" &amp; output="test_tbcompositejsontable2"</t>
+          <t>full_name="test.TbCompositeJsonTable2" &amp; input="*table2@test/composite_tables.json"</t>
         </is>
       </c>
     </row>
